--- a/PK-aplicativos-detalle.xlsx
+++ b/PK-aplicativos-detalle.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\x16267\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71FFC02E-3FCB-4A7D-A41F-75A0DAD7141B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A8526E-08E6-4BB0-9185-1C47AE00CE1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{147BDDF4-11B9-4048-ACC4-453260DDCBC7}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="45">
   <si>
     <t>Aplicativo</t>
   </si>
@@ -107,30 +107,18 @@
     <t>$ST</t>
   </si>
   <si>
-    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CLIE||p01_fi_docu||p01_co_prod||p01_id_docu</t>
-  </si>
-  <si>
     <t>CDO</t>
   </si>
   <si>
     <t>Montos dentro de PK y filas repetidas</t>
   </si>
   <si>
-    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||P01_ID_CAMP_08||P01_ID_CLIE||p01_fi_docu||p01_id_docu||P01_IM_INTERES||P01_IM_COMISIONES||P01_IM_SALD</t>
-  </si>
-  <si>
     <t>FMU</t>
   </si>
   <si>
-    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||P01_ID_CAMP_08||P01_ID_CLIE||p01_fi_docu||p01_co_prod||p01_id_docu</t>
-  </si>
-  <si>
     <t>GAC</t>
   </si>
   <si>
-    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||P01_ID_CAMP_08||P01_ID_CLIE||p01_fi_docu||p01_co_prod||p01_id_docu||APRFCRO_NU_DOCU_GAR_BAS</t>
-  </si>
-  <si>
     <t>PRO</t>
   </si>
   <si>
@@ -140,15 +128,9 @@
     <t>JCC</t>
   </si>
   <si>
-    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||P01_ID_CAMP_08||||p01_id_docu</t>
-  </si>
-  <si>
     <t>LID</t>
   </si>
   <si>
-    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||P01_ID_CAMP_08||P01_ID_CLIE||p01_fi_docu||p01_co_prod||p01_id_docu||P01_NU_DOCU</t>
-  </si>
-  <si>
     <t>ADJ</t>
   </si>
   <si>
@@ -156,6 +138,42 @@
   </si>
   <si>
     <t>Solo 1 fila, puros campos null</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01|| P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_DOCU</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CLIE||P01_ID_DOCU</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||P01_ID_CAMP_08||P01_ID_DOCU||P01_IM_INTERES||P01_IM_COMISIONES||P01_IM_SALD</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01|| P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||P01_ID_CAMP_08||P01_ID_CAMP_09||P01_ID_CAMP_10||P01_ID_DOCU</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01|| P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||P01_ID_DOCU</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01||P01_ID_CLIE||p01_id_docu</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||P01_ID_CAMP_08||p01_id_docu||APRFCRO_NU_DOCU_GAR_BAS</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||p01_id_docu</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01||P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CLIE||p01_fi_docu||p01_co_prod||p01_id_docu||P01_NU_DOCU</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01|| P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_CAMP_05||P01_ID_CAMP_06||P01_ID_CAMP_07||P01_ID_CAMP_08||P01_ID_CAMP_09||P01_ID_DOCU</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01|| P01_ID_CAMP_02||P01_ID_CAMP_03||P01_ID_CAMP_04||P01_ID_DOCU</t>
+  </si>
+  <si>
+    <t>P01_ID_CAMP_01||P01_ID_DOCU</t>
   </si>
 </sst>
 </file>
@@ -179,12 +197,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -199,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -215,6 +239,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -269,13 +296,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{32A47AF6-010B-4E25-81CC-B4940AA584A9}" name="Tabla8" displayName="Tabla8" ref="A1:D22" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
-  <autoFilter ref="A1:D22" xr:uid="{32A47AF6-010B-4E25-81CC-B4940AA584A9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{64074E09-ECA4-40CD-A225-228B23C38C38}" name="Tabla83" displayName="Tabla83" ref="A1:D22" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
+  <autoFilter ref="A1:D22" xr:uid="{64074E09-ECA4-40CD-A225-228B23C38C38}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D22">
+    <sortCondition ref="A1:A22"/>
+  </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{73247421-C104-47D3-92CA-1BA87A4F749A}" name="Aplicativo" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{D72CFB42-6ED3-4B39-8619-C03AB9C16781}" name="Estado" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{69F942D4-0C23-44FF-A3BA-C030931B2383}" name="Casos especiales" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{FB990F9A-49E7-4DBE-A94F-EB668C12FF58}" name="PK" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{E2E5ACC5-FFC6-4638-ABD0-21C77FE8DAF1}" name="Aplicativo" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{05055CD0-1A02-45C7-BD32-5C8590B5D05A}" name="Estado" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{65FE4E45-D1DB-46FE-9274-AEF98B5CD979}" name="Casos especiales" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{E8F6C033-85DD-4D97-A7DB-A826612CC7B0}" name="PK" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -622,43 +652,45 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="3" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
+      <c r="A3" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="3" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>8</v>
+      <c r="A4" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="D4" s="3" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
-        <v>9</v>
+      <c r="A5" s="6" t="s">
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>5</v>
@@ -669,213 +701,211 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
-        <v>12</v>
+      <c r="A8" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="3" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
-        <v>13</v>
+      <c r="A9" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="3" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
+      <c r="A10" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="3" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="3" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="3" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>19</v>
-      </c>
+      <c r="C14" s="4"/>
       <c r="D14" s="3" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="3" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>24</v>
-      </c>
+      <c r="C16" s="4"/>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="D18" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C19" s="4"/>
       <c r="D19" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C20" s="4"/>
       <c r="D20" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C22" s="4"/>
       <c r="D22" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
